--- a/CorrectionExemplesHAS/ig/StructureDefinition-fr-treatment-intent.xlsx
+++ b/CorrectionExemplesHAS/ig/StructureDefinition-fr-treatment-intent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T09:32:00+00:00</t>
+    <t>2025-11-07T09:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CorrectionExemplesHAS/ig/StructureDefinition-fr-treatment-intent.xlsx
+++ b/CorrectionExemplesHAS/ig/StructureDefinition-fr-treatment-intent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T09:34:21+00:00</t>
+    <t>2025-11-07T09:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
